--- a/data/trans_orig/IQ14-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ14-Habitat-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Número de días que los menores se han tenido que quedar en la cama más de medio día por motivos de salud</t>
+          <t>Número de días que los menores se han tenido que quedar en la cama más de medio día por motivos de salud (tasa de respuesta: 97,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,32 +716,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,66; 6,79</t>
+          <t>1,64; 6,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,49; 4,05</t>
+          <t>1,53; 3,91</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,35; 5,19</t>
+          <t>1,45; 5,46</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,37; 6,03</t>
+          <t>2,34; 6,04</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,35; 7,85</t>
+          <t>2,37; 8,21</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,49; 4,02</t>
+          <t>1,46; 3,59</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -751,27 +751,27 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,55; 8,71</t>
+          <t>4,51; 8,41</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,33; 6,41</t>
+          <t>2,37; 6,15</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,66; 3,26</t>
+          <t>1,64; 3,35</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,28; 3,89</t>
+          <t>1,34; 3,7</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,9; 6,77</t>
+          <t>3,93; 6,72</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,46; 3,32</t>
+          <t>1,46; 3,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,57; 3,73</t>
+          <t>1,56; 3,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,51; 6,41</t>
+          <t>2,5; 6,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,82; 4,93</t>
+          <t>2,88; 4,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,68; 3,47</t>
+          <t>1,65; 3,33</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,68; 4,47</t>
+          <t>1,63; 4,03</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,47; 2,52</t>
+          <t>1,47; 2,63</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,79; 12,8</t>
+          <t>4,49; 12,65</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,78; 2,97</t>
+          <t>1,73; 2,89</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,76; 3,38</t>
+          <t>1,78; 3,27</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,16; 4,26</t>
+          <t>2,11; 4,06</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,18; 9,09</t>
+          <t>4,18; 9,13</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,64; 2,96</t>
+          <t>1,6; 2,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,87; 5,59</t>
+          <t>1,81; 5,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,32; 1,93</t>
+          <t>1,33; 1,93</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,34; 6,14</t>
+          <t>2,37; 6,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,3; 1,98</t>
+          <t>1,29; 1,97</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,66; 4,48</t>
+          <t>1,71; 4,62</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,58; 3,25</t>
+          <t>1,59; 3,29</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,15; 3,64</t>
+          <t>2,15; 3,65</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,57; 2,4</t>
+          <t>1,57; 2,38</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,99; 4,02</t>
+          <t>1,99; 4,15</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,56; 2,58</t>
+          <t>1,56; 2,5</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,52; 4,49</t>
+          <t>2,51; 4,61</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,77; 11,24</t>
+          <t>2,1; 11,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,81; 3,88</t>
+          <t>1,79; 3,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,97; 4,02</t>
+          <t>1,9; 3,97</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,03; 5,11</t>
+          <t>3,04; 5,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,1; 4,87</t>
+          <t>2,01; 4,79</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,52; 4,89</t>
+          <t>1,5; 4,96</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,27; 2,46</t>
+          <t>1,32; 2,47</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,95; 6,33</t>
+          <t>2,98; 6,23</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,33; 5,61</t>
+          <t>2,42; 5,68</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,88; 4,01</t>
+          <t>1,82; 4,05</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,86; 3,36</t>
+          <t>1,88; 3,57</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,33; 5,6</t>
+          <t>3,42; 5,62</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,08; 4,2</t>
+          <t>2,09; 3,93</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,04; 3,24</t>
+          <t>2,08; 3,32</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,23; 3,78</t>
+          <t>2,27; 3,83</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,2; 4,7</t>
+          <t>3,18; 4,63</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,22; 3,68</t>
+          <t>2,15; 3,5</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,91; 3,3</t>
+          <t>1,92; 3,24</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,58; 2,31</t>
+          <t>1,61; 2,35</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,92; 6,65</t>
+          <t>3,99; 6,87</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,27; 3,44</t>
+          <t>2,26; 3,4</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,13; 3,0</t>
+          <t>2,12; 3,03</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,03; 2,9</t>
+          <t>2,01; 2,9</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,88; 5,61</t>
+          <t>3,89; 5,5</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ14-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ14-Habitat-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Número de días que los menores se han tenido que quedar en la cama más de medio día por motivos de salud (tasa de respuesta: 97,77%)</t>
+          <t>Tiempo demio en días que en las últimas 2 semanas los menores se han tenido que quedar en la cama más de medio día por motivos de salud (tasa de respuesta: 97,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,64; 6,95</t>
+          <t>1,63; 6,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,53; 3,91</t>
+          <t>1,52; 3,79</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,45; 5,46</t>
+          <t>1,44; 5,46</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,34; 6,04</t>
+          <t>2,48; 6,01</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,37; 8,21</t>
+          <t>2,46; 8,13</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,46; 3,59</t>
+          <t>1,44; 3,8</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,84</t>
+          <t>1,0; 1,79</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,51; 8,41</t>
+          <t>4,47; 8,52</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,37; 6,15</t>
+          <t>2,52; 6,16</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,64; 3,35</t>
+          <t>1,62; 3,2</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,34; 3,7</t>
+          <t>1,35; 3,87</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,93; 6,72</t>
+          <t>3,84; 6,71</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,46; 3,1</t>
+          <t>1,46; 3,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,56; 3,84</t>
+          <t>1,62; 3,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,5; 6,51</t>
+          <t>2,54; 6,43</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,88; 4,92</t>
+          <t>2,85; 4,99</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,65; 3,33</t>
+          <t>1,74; 3,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,63; 4,03</t>
+          <t>1,67; 4,16</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,47; 2,63</t>
+          <t>1,48; 2,63</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,49; 12,65</t>
+          <t>4,51; 12,76</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,73; 2,89</t>
+          <t>1,72; 2,97</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,78; 3,27</t>
+          <t>1,77; 3,36</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,11; 4,06</t>
+          <t>2,12; 4,27</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,18; 9,13</t>
+          <t>4,04; 9,18</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,6; 2,92</t>
+          <t>1,59; 2,93</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,81; 5,54</t>
+          <t>1,85; 5,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,33; 1,93</t>
+          <t>1,34; 1,93</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,37; 6,1</t>
+          <t>2,31; 5,89</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,29; 1,97</t>
+          <t>1,29; 2,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,71; 4,62</t>
+          <t>1,78; 4,66</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,59; 3,29</t>
+          <t>1,58; 3,22</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,15; 3,65</t>
+          <t>2,12; 3,55</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,57; 2,38</t>
+          <t>1,54; 2,36</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,99; 4,15</t>
+          <t>2,0; 4,18</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,56; 2,5</t>
+          <t>1,56; 2,51</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,51; 4,61</t>
+          <t>2,5; 4,42</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,1; 11,8</t>
+          <t>2,1; 11,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,79; 3,87</t>
+          <t>1,82; 3,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,9; 3,97</t>
+          <t>1,91; 4,04</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,04; 5,21</t>
+          <t>3,1; 5,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,01; 4,79</t>
+          <t>2,03; 4,71</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,5; 4,96</t>
+          <t>1,52; 5,25</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,32; 2,47</t>
+          <t>1,28; 2,46</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,98; 6,23</t>
+          <t>2,97; 6,3</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,42; 5,68</t>
+          <t>2,39; 5,52</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,82; 4,05</t>
+          <t>1,88; 4,01</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,88; 3,57</t>
+          <t>1,85; 3,36</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,42; 5,62</t>
+          <t>3,43; 5,57</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,09; 3,93</t>
+          <t>2,03; 3,92</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,08; 3,32</t>
+          <t>2,03; 3,23</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,27; 3,83</t>
+          <t>2,26; 3,87</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,18; 4,63</t>
+          <t>3,25; 4,72</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,15; 3,5</t>
+          <t>2,14; 3,6</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,92; 3,24</t>
+          <t>1,94; 3,29</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,61; 2,35</t>
+          <t>1,62; 2,28</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,99; 6,87</t>
+          <t>3,97; 6,69</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,26; 3,4</t>
+          <t>2,27; 3,39</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,12; 3,03</t>
+          <t>2,12; 3,0</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,01; 2,9</t>
+          <t>2,04; 2,98</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,89; 5,5</t>
+          <t>3,88; 5,51</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ14-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ14-Habitat-trans_orig.xlsx
@@ -526,13 +526,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tiempo demio en días que en las últimas 2 semanas los menores se han tenido que quedar en la cama más de medio día por motivos de salud (tasa de respuesta: 97,77%)</t>
+          <t>Tiempo medio en días que en las últimas 2 semanas los menores se han tenido que quedar en la cama más de medio día por motivos de salud (tasa de respuesta: 97,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -540,7 +540,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -648,42 +648,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4,33</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2,09</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1,24</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6,34</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>3,52</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>2,32</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>2,92</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4,13</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>4,33</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,09</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,24</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>6,24</t>
+          <t>4,15</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,25</t>
+          <t>5,28</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,63; 6,98</t>
+          <t>2,35; 7,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,52; 3,79</t>
+          <t>1,49; 4,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,44; 5,46</t>
+          <t>1,0; 1,84</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,48; 6,01</t>
+          <t>4,7; 8,84</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,46; 8,13</t>
+          <t>1,66; 6,79</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,44; 3,8</t>
+          <t>1,49; 4,05</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,79</t>
+          <t>1,35; 5,19</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,47; 8,52</t>
+          <t>2,35; 6,04</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,52; 6,16</t>
+          <t>2,33; 6,41</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,62; 3,2</t>
+          <t>1,66; 3,26</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,35; 3,87</t>
+          <t>1,28; 3,89</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,84; 6,71</t>
+          <t>3,87; 6,82</t>
         </is>
       </c>
     </row>
@@ -788,54 +788,54 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>2,34</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2,34</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1,89</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>7,59</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>2,04</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>2,33</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>3,9</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>3,82</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>3,79</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>2,21</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>2,34</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>2,34</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>1,89</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>7,34</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>2,21</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>2,34</t>
-        </is>
-      </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
           <t>2,89</t>
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5,8</t>
+          <t>5,99</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,46; 3,18</t>
+          <t>1,68; 3,47</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,62; 3,96</t>
+          <t>1,68; 4,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,54; 6,43</t>
+          <t>1,47; 2,52</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,85; 4,99</t>
+          <t>5,04; 13,08</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,74; 3,4</t>
+          <t>1,46; 3,32</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,67; 4,16</t>
+          <t>1,57; 3,73</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,48; 2,63</t>
+          <t>2,51; 6,41</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,51; 12,76</t>
+          <t>2,82; 4,91</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,72; 2,97</t>
+          <t>1,78; 2,97</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,77; 3,36</t>
+          <t>1,76; 3,38</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,12; 4,27</t>
+          <t>2,16; 4,26</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,04; 9,18</t>
+          <t>4,28; 9,4</t>
         </is>
       </c>
     </row>
@@ -928,54 +928,54 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1,61</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2,56</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2,18</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2,77</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>2,04</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>3,31</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>1,62</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3,55</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1,61</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>2,56</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2,18</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
+          <t>3,57</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1,85</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
           <t>2,8</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>1,85</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>2,8</t>
-        </is>
-      </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
           <t>1,91</t>
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,14</t>
+          <t>3,16</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,59; 2,93</t>
+          <t>1,3; 1,98</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,85; 5,63</t>
+          <t>1,66; 4,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,34; 1,93</t>
+          <t>1,58; 3,25</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,31; 5,89</t>
+          <t>2,12; 3,62</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,29; 2,01</t>
+          <t>1,64; 2,96</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,78; 4,66</t>
+          <t>1,87; 5,59</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,58; 3,22</t>
+          <t>1,32; 1,93</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,12; 3,55</t>
+          <t>2,36; 6,16</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,54; 2,36</t>
+          <t>1,57; 2,4</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,0; 4,18</t>
+          <t>1,99; 4,02</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,56; 2,51</t>
+          <t>1,56; 2,58</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,5; 4,42</t>
+          <t>2,51; 4,59</t>
         </is>
       </c>
     </row>
@@ -1068,42 +1068,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3,03</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2,56</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1,83</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4,41</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>5,07</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>2,63</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>2,69</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4,05</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>3,03</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,56</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,83</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>4,5</t>
+          <t>3,95</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,32</t>
+          <t>4,22</t>
         </is>
       </c>
     </row>
@@ -1136,47 +1136,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,1; 11,25</t>
+          <t>2,1; 4,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,82; 3,8</t>
+          <t>1,52; 4,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,91; 4,04</t>
+          <t>1,27; 2,46</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,1; 5,07</t>
+          <t>2,9; 6,18</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,03; 4,71</t>
+          <t>1,77; 11,24</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,52; 5,25</t>
+          <t>1,81; 3,88</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,28; 2,46</t>
+          <t>1,97; 4,02</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,97; 6,3</t>
+          <t>2,96; 5,01</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,39; 5,52</t>
+          <t>2,33; 5,61</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1186,12 +1186,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,85; 3,36</t>
+          <t>1,86; 3,36</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,43; 5,57</t>
+          <t>3,25; 5,43</t>
         </is>
       </c>
     </row>
@@ -1208,42 +1208,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>2,72</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2,43</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1,89</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>5,12</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>2,77</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>2,58</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>2,84</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>3,84</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>2,72</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>2,43</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>1,89</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5,01</t>
+          <t>3,81</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4,5</t>
+          <t>4,54</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,03; 3,92</t>
+          <t>2,22; 3,68</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,03; 3,23</t>
+          <t>1,91; 3,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,26; 3,87</t>
+          <t>1,58; 2,31</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,25; 4,72</t>
+          <t>4,0; 6,87</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,14; 3,6</t>
+          <t>2,08; 4,2</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,94; 3,29</t>
+          <t>2,04; 3,24</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,62; 2,28</t>
+          <t>2,23; 3,78</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,97; 6,69</t>
+          <t>3,17; 4,72</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,27; 3,39</t>
+          <t>2,27; 3,44</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,12; 3,0</t>
+          <t>2,13; 3,0</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,04; 2,98</t>
+          <t>2,03; 2,9</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,88; 5,51</t>
+          <t>3,86; 5,59</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ14-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ14-Habitat-trans_orig.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +140,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -646,419 +651,271 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>4,33</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2,09</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1,24</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6,34</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>3,52</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,32</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,92</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>4,15</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>3,9</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>2,22</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2,07</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>5,28</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>4.330626880734766</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>2.088966251891268</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>1.237096406706198</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>6.340904001529027</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>3.516871389240458</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>2.324988740911007</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>2.919772951719207</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>4.152705812254069</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>3.89658852100414</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>2.21730151008065</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>2.071183234665552</v>
+      </c>
+      <c r="N4" s="5" t="n">
+        <v>5.284157693965924</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>2,35; 7,85</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>1,49; 4,02</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>1,0; 1,84</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>4,7; 8,84</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1,66; 6,79</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>1,49; 4,05</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>1,35; 5,19</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>2,35; 6,04</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>2,33; 6,41</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>1,66; 3,26</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>1,28; 3,89</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>3,87; 6,82</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>2.347682712005696</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>1.494322933671847</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>4.695799271364907</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>1.661708991194623</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>1.488721251102765</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>1.352513496806151</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>2.351906761227162</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>2.330516890371977</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>1.661290127499032</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>1.280466499397309</v>
+      </c>
+      <c r="N5" s="5" t="n">
+        <v>3.873109858118388</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>7.845113112251743</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>4.017339237803381</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>1.843343136924664</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>8.835311267081558</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>6.793166003920364</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>4.046642730782584</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>5.18578544775287</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>6.039311980008537</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>6.41109339468847</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>3.261232049602282</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>3.887806940335239</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>6.823262755489811</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>2,34</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>2,34</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1,89</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>7,59</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>2,04</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>2,33</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>3,9</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>3,79</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>2,21</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>2,34</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>2,89</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>5,99</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>1,68; 3,47</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>1,68; 4,47</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1,47; 2,52</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>5,04; 13,08</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>1,46; 3,32</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,57; 3,73</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2,51; 6,41</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2,82; 4,91</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1,78; 2,97</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1,76; 3,38</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>2,16; 4,26</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>4,28; 9,4</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>2.338474785313364</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>2.337774408563321</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>1.887097572286542</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>7.588313411723546</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>2.035859119168871</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>2.333348464569403</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>3.899318183379421</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>3.785411435760836</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>2.205115852075958</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>2.335456280878215</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>2.894817338969524</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>5.986031486641024</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>1,61</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>2,56</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>2,18</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2,77</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2,04</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>3,31</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>1,62</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>3,57</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>1,85</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>2,8</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>1,91</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>3,16</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>1.676788900027943</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>1.676699215920084</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>1.471466297886137</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>5.041203055336925</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>1.461224884010434</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>1.571071276095726</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>2.509241683926869</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>2.824546776409836</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>1.775233323479748</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>1.764590435792882</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>2.162882487640796</v>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>4.284674841876117</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>1,3; 1,98</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>1,66; 4,48</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>1,58; 3,25</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>2,12; 3,62</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>1,64; 2,96</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>1,87; 5,59</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>1,32; 1,93</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>2,36; 6,16</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>1,57; 2,4</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>1,99; 4,02</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>1,56; 2,58</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>2,51; 4,59</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>3.465495167868712</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>4.47100209545911</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>2.518537223928497</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>13.08021547859794</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>3.318877598905097</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>3.7343299161388</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>6.414627745403267</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>4.914213156375714</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>2.973946442595752</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>3.378799264981302</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>4.262173256160984</v>
+      </c>
+      <c r="N9" s="5" t="n">
+        <v>9.400268487739121</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1066,277 +923,405 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>3,03</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>2,56</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1,83</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4,41</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>5,07</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,63</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,69</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>3,95</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>3,61</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>2,59</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>2,4</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>4,22</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>1.607322674751703</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>2.55859587454476</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>2.180720456454184</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>2.765466398048857</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>2.040982557522645</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>3.310629737460668</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>1.615700208199483</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>3.57104144331977</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>1.849192298132732</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>2.799204303944333</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>1.913756854126487</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>3.157443312575731</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>2,1; 4,87</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>1,52; 4,89</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>1,27; 2,46</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>2,9; 6,18</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>1,77; 11,24</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>1,81; 3,88</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>1,97; 4,02</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>2,96; 5,01</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>2,33; 5,61</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>1,88; 4,01</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>1,86; 3,36</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>3,25; 5,43</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>1.295111470050538</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>1.662504310486521</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>1.576303588498079</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>2.119848280360533</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>1.643722609705792</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>1.871041730518581</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>1.319882504740292</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>2.356631411887202</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>1.567143891793491</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>1.9865516737003</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>1.563777692932061</v>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>2.51482430710718</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>1.976532306999942</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>4.484270871737237</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>3.254686579623363</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>3.621095289118144</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>2.959377234540874</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>5.587796331019961</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>1.931107734576531</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>6.162926359803597</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>2.403641078765098</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>4.024480821057808</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>2.581296072800418</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>4.590531305310761</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>3.029986101662187</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>2.563863431422106</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>1.834344299131446</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>4.41120021149527</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>5.074150201439917</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>2.633903875993405</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>2.693168755918269</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>3.947079376611583</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>3.607574731604084</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>2.593837178391218</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>2.396569615657977</v>
+      </c>
+      <c r="N13" s="5" t="n">
+        <v>4.220907926301128</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>2.100084344133989</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>1.519323150286529</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>1.270285425187346</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>2.900451810721231</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>1.769053798525705</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>1.80819196979468</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>1.9709061641633</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>2.96223761603019</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>2.331062138546697</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>1.882511034361465</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>1.855125198980807</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>3.250548585731185</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>4.86809251625109</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>4.88629929083779</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>2.46093351389659</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>6.180967896308176</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>11.23901580247802</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>3.875721227349156</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>4.015945612260511</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>5.007868142001226</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>5.60730493273558</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>4.007683944839246</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>3.360347026316836</v>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>5.426957287168035</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>2,72</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>2,43</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1,89</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>5,12</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>2,77</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>2,58</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>2,84</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>3,81</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>2,74</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>2,5</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>2,39</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>4,54</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>2,22; 3,68</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>1,91; 3,3</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1,58; 2,31</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4,0; 6,87</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>2,08; 4,2</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2,04; 3,24</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,23; 3,78</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>3,17; 4,72</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>2,27; 3,44</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>2,13; 3,0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>2,03; 2,9</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>3,86; 5,59</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>2.7157473084031</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>2.426476008722199</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>1.888457339479541</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>5.119087206083094</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>2.765330607319737</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>2.581378663833384</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>2.836747089976419</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>3.81203381734404</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>2.738368050166753</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>2.496365718461826</v>
+      </c>
+      <c r="M16" s="5" t="n">
+        <v>2.389753085717961</v>
+      </c>
+      <c r="N16" s="5" t="n">
+        <v>4.535792516445901</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>2.219361632368277</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>1.909241447837609</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>1.580688733570163</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>3.99926108856692</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>2.083811240031952</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>2.03676227362654</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>2.232357368784571</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>3.16509917571241</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>2.265020926931364</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>2.125380395995036</v>
+      </c>
+      <c r="M17" s="5" t="n">
+        <v>2.031956874367103</v>
+      </c>
+      <c r="N17" s="5" t="n">
+        <v>3.862592635105313</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>3.675658098589313</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>3.298807477853323</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>2.308832055243021</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>6.86776841469084</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>4.195253122394644</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>3.236412504667187</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>3.783151226843438</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>4.7216976878265</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>3.439103805410435</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>2.999988775499292</v>
+      </c>
+      <c r="M18" s="5" t="n">
+        <v>2.897774504835769</v>
+      </c>
+      <c r="N18" s="5" t="n">
+        <v>5.594812000573126</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1344,15 +1329,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
     <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
